--- a/public/static/参演人员导入模板1.xlsx
+++ b/public/static/参演人员导入模板1.xlsx
@@ -40,7 +40,7 @@
     <t>姓名</t>
   </si>
   <si>
-    <t>身份证</t>
+    <t>身份证后6位</t>
   </si>
   <si>
     <t>年龄</t>
